--- a/resources/practica5/tiempos.xlsx
+++ b/resources/practica5/tiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\informatica-30717.github.io\resources\practica5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79529D9F-E784-47C6-8B79-E60D7E740789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F54935-3A11-4C8E-B1A9-1195CC11C3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7D39335-D069-4A90-893C-03F30C90014F}"/>
   </bookViews>
